--- a/public/reports/philips/weekly-feedback-historical-import-template.xlsx
+++ b/public/reports/philips/weekly-feedback-historical-import-template.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14080" yWindow="600" windowWidth="13320" windowHeight="16480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Feedback Import" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,8 +25,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -39,7 +41,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000B1B3A"/>
+        <fgColor rgb="FF0B1B3A"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,7 +62,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -423,8 +425,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -484,147 +486,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Clicks Store Survey</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Philips PH</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Gauteng</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Mmuluki  Makhurane</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Male Grooming</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Parkrand</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>QP1424 available?</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Checkers Instore Survey</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Philips PH</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Western Cape</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Enver De Bruyn</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Beauty</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CHECKERS HYPER CH N1 CITY</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PHILIPS FACIAL HAIR REMOVER BRR454 BRL136 - Listed?</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dischem Store Audit</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Philips PH</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>KwaZulu-Natal</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Nicholas Haripershad</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Beauty</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dischem Galleria Mall</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Is there a beauty standout display in beauty to differentiate product within regular shelf/endcap?</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
